--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-21.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-21.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="273">
   <si>
     <t>Date: 2024-11-21</t>
   </si>
@@ -59,106 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Shree Krishna Securities Limited</t>
-  </si>
-  <si>
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Agrawal Securities Pvt. Limited</t>
+    <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
-    <t>Investment Management Nepal Pvt. Ltd.</t>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
   </si>
   <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Premier Securites Company Limited</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>45</t>
   </si>
   <si>
-    <t>53</t>
+    <t>41</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>57</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2,118,263,972.6</t>
-  </si>
-  <si>
-    <t>996,825,964.8</t>
-  </si>
-  <si>
-    <t>563,532,303.6</t>
-  </si>
-  <si>
-    <t>502,963,183.29</t>
-  </si>
-  <si>
-    <t>501,625,660.9</t>
-  </si>
-  <si>
-    <t>500,114,621.1</t>
-  </si>
-  <si>
-    <t>495,641,686.5</t>
-  </si>
-  <si>
-    <t>2,017,892,695.6</t>
-  </si>
-  <si>
-    <t>393,782,370.7</t>
-  </si>
-  <si>
-    <t>153,078,748.0</t>
-  </si>
-  <si>
-    <t>294,538,426.2</t>
-  </si>
-  <si>
-    <t>51,335,626.5</t>
-  </si>
-  <si>
-    <t>273,210,364.0</t>
-  </si>
-  <si>
-    <t>242,182,332.2</t>
-  </si>
-  <si>
-    <t>100,371,277.0</t>
-  </si>
-  <si>
-    <t>603,043,594.1</t>
-  </si>
-  <si>
-    <t>410,453,555.6</t>
-  </si>
-  <si>
-    <t>208,424,757.1</t>
-  </si>
-  <si>
-    <t>450,290,034.4</t>
-  </si>
-  <si>
-    <t>226,904,257.1</t>
-  </si>
-  <si>
-    <t>253,459,354.3</t>
+    <t>1,010,533,802.9</t>
+  </si>
+  <si>
+    <t>645,414,056.72</t>
+  </si>
+  <si>
+    <t>622,826,166.97</t>
+  </si>
+  <si>
+    <t>534,724,421.0</t>
+  </si>
+  <si>
+    <t>499,989,071.4</t>
+  </si>
+  <si>
+    <t>499,759,611.42</t>
+  </si>
+  <si>
+    <t>494,191,450.39</t>
+  </si>
+  <si>
+    <t>483,754,318.45</t>
+  </si>
+  <si>
+    <t>300,136,238.22</t>
+  </si>
+  <si>
+    <t>266,457,084.5</t>
+  </si>
+  <si>
+    <t>186,923,050.3</t>
+  </si>
+  <si>
+    <t>242,606,475.8</t>
+  </si>
+  <si>
+    <t>285,335,705.7</t>
+  </si>
+  <si>
+    <t>246,964,088.9</t>
+  </si>
+  <si>
+    <t>526,779,484.45</t>
+  </si>
+  <si>
+    <t>345,277,818.5</t>
+  </si>
+  <si>
+    <t>356,369,082.47</t>
+  </si>
+  <si>
+    <t>347,801,370.7</t>
+  </si>
+  <si>
+    <t>257,382,595.6</t>
+  </si>
+  <si>
+    <t>214,423,905.73</t>
+  </si>
+  <si>
+    <t>247,227,361.49</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -176,376 +179,322 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>USHEC</t>
-  </si>
-  <si>
-    <t>1,939,200,000.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>30,326,400.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>28,572,570.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>4,134,535.2</t>
-  </si>
-  <si>
-    <t>ADBL</t>
-  </si>
-  <si>
-    <t>4,066,560.0</t>
-  </si>
-  <si>
-    <t>SMB</t>
-  </si>
-  <si>
-    <t>85,742,187.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>77,704,997.0</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>42,071,904.0</t>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>74,549,405.9</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>32,157,593.9</t>
+  </si>
+  <si>
+    <t>MLBBL</t>
+  </si>
+  <si>
+    <t>31,032,619.0</t>
+  </si>
+  <si>
+    <t>MBJC</t>
+  </si>
+  <si>
+    <t>25,198,951.4</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>16,136,459.7</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>22,326,068.4</t>
+  </si>
+  <si>
+    <t>16,098,377.0</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>15,386,737.5</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>13,551,613.3</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>10,460,784.8</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>16,061,144.0</t>
+  </si>
+  <si>
+    <t>8,774,225.4</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>8,035,345.5</t>
+  </si>
+  <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>7,242,719.5</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>5,547,785.2</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>58,100,168.5</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>13,623,450.5</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>4,629,203.2</t>
+  </si>
+  <si>
+    <t>3,659,137.0</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>2,922,980.0</t>
+  </si>
+  <si>
+    <t>10,240,471.1</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>9,354,480.0</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>7,819,918.0</t>
+  </si>
+  <si>
+    <t>7,106,209.0</t>
+  </si>
+  <si>
+    <t>6,495,789.8</t>
+  </si>
+  <si>
+    <t>20,679,450.89</t>
+  </si>
+  <si>
+    <t>10,797,172.2</t>
+  </si>
+  <si>
+    <t>10,097,373.9</t>
+  </si>
+  <si>
+    <t>5,398,321.5</t>
+  </si>
+  <si>
+    <t>TAMOR</t>
+  </si>
+  <si>
+    <t>5,258,976.0</t>
+  </si>
+  <si>
+    <t>7,400,589.9</t>
+  </si>
+  <si>
+    <t>LBBL</t>
+  </si>
+  <si>
+    <t>6,434,708.3</t>
+  </si>
+  <si>
+    <t>HHL</t>
+  </si>
+  <si>
+    <t>6,026,803.0</t>
+  </si>
+  <si>
+    <t>5,098,144.4</t>
+  </si>
+  <si>
+    <t>4,923,422.3</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>88,631,597.1</t>
+  </si>
+  <si>
+    <t>28,917,820.0</t>
+  </si>
+  <si>
+    <t>19,796,311.1</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>15,953,612.0</t>
+  </si>
+  <si>
+    <t>NMLBBL</t>
+  </si>
+  <si>
+    <t>15,375,420.4</t>
+  </si>
+  <si>
+    <t>SINDU</t>
+  </si>
+  <si>
+    <t>10,413,332.8</t>
+  </si>
+  <si>
+    <t>10,252,942.69</t>
+  </si>
+  <si>
+    <t>ILBS</t>
+  </si>
+  <si>
+    <t>8,587,808.6</t>
+  </si>
+  <si>
+    <t>7,410,359.3</t>
+  </si>
+  <si>
+    <t>6,561,379.5</t>
+  </si>
+  <si>
+    <t>14,068,127.9</t>
+  </si>
+  <si>
+    <t>12,725,852.2</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>11,796,820.0</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>8,402,079.0</t>
+  </si>
+  <si>
+    <t>7,194,364.3</t>
+  </si>
+  <si>
+    <t>129,000,339.6</t>
+  </si>
+  <si>
+    <t>67,249,546.5</t>
+  </si>
+  <si>
+    <t>44,035,510.3</t>
+  </si>
+  <si>
+    <t>4,111,945.5</t>
+  </si>
+  <si>
+    <t>3,374,783.5</t>
+  </si>
+  <si>
+    <t>13,349,351.5</t>
+  </si>
+  <si>
+    <t>8,375,533.3</t>
+  </si>
+  <si>
+    <t>7,632,337.0</t>
+  </si>
+  <si>
+    <t>7,318,882.5</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>7,076,036.3</t>
+  </si>
+  <si>
+    <t>14,892,343.8</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>5,816,707.7</t>
   </si>
   <si>
     <t>GBIME</t>
   </si>
   <si>
-    <t>29,338,148.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>21,449,300.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>74,320,000.0</t>
-  </si>
-  <si>
-    <t>44,881,500.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>8,157,000.0</t>
-  </si>
-  <si>
-    <t>5,769,600.0</t>
-  </si>
-  <si>
-    <t>MKHL</t>
-  </si>
-  <si>
-    <t>5,472,000.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>121,232,565.0</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>71,618,550.0</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>18,727,200.0</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>17,888,659.0</t>
-  </si>
-  <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>16,995,200.0</t>
-  </si>
-  <si>
-    <t>42,432,000.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>2,275,200.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>1,168,179.0</t>
-  </si>
-  <si>
-    <t>NMFBS</t>
-  </si>
-  <si>
-    <t>965,864.0</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>752,320.0</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>79,886,400.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>39,779,225.0</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>27,223,503.3</t>
-  </si>
-  <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>22,880,600.0</t>
-  </si>
-  <si>
-    <t>21,373,186.0</t>
-  </si>
-  <si>
-    <t>43,049,568.0</t>
-  </si>
-  <si>
-    <t>42,276,000.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>35,040,000.0</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>34,980,362.6</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>24,590,725.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>40,640,000.0</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>36,480,160.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>16,615,650.0</t>
-  </si>
-  <si>
-    <t>DOLTI</t>
-  </si>
-  <si>
-    <t>1,867,200.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>1,113,600.0</t>
-  </si>
-  <si>
-    <t>178,140,090.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>80,999,560.0</t>
-  </si>
-  <si>
-    <t>76,238,145.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>50,067,343.2</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>40,033,536.0</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>152,156,750.0</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>80,660,160.0</t>
-  </si>
-  <si>
-    <t>60,032,770.0</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>52,070,400.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>33,600,000.0</t>
-  </si>
-  <si>
-    <t>BHPL</t>
-  </si>
-  <si>
-    <t>58,606,300.0</t>
-  </si>
-  <si>
-    <t>43,522,600.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>28,379,084.0</t>
-  </si>
-  <si>
-    <t>19,528,960.0</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>15,763,200.0</t>
-  </si>
-  <si>
-    <t>445,290,080.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>1,580,144.0</t>
-  </si>
-  <si>
-    <t>PRIN</t>
-  </si>
-  <si>
-    <t>631,101.6</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>440,800.0</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>298,300.0</t>
-  </si>
-  <si>
-    <t>116,800,000.0</t>
-  </si>
-  <si>
-    <t>NMLBBL</t>
-  </si>
-  <si>
-    <t>17,232,000.0</t>
-  </si>
-  <si>
-    <t>NICLBSL</t>
-  </si>
-  <si>
-    <t>13,691,840.0</t>
-  </si>
-  <si>
-    <t>JSLBB</t>
-  </si>
-  <si>
-    <t>13,608,500.0</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>13,057,120.0</t>
-  </si>
-  <si>
-    <t>UNLB</t>
-  </si>
-  <si>
-    <t>216,199,542.0</t>
-  </si>
-  <si>
-    <t>4,195,530.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>3,285,312.0</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>2,296,320.0</t>
+    <t>5,410,816.9</t>
+  </si>
+  <si>
+    <t>GBBL</t>
+  </si>
+  <si>
+    <t>5,206,238.3</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>4,332,474.09</t>
+  </si>
+  <si>
+    <t>9,045,632.6</t>
+  </si>
+  <si>
+    <t>8,632,416.19</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>8,319,072.7</t>
+  </si>
+  <si>
+    <t>TSHL</t>
+  </si>
+  <si>
+    <t>6,854,755.7</t>
+  </si>
+  <si>
+    <t>6,154,557.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -563,106 +512,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>1,987,896,283.9</t>
-  </si>
-  <si>
-    <t>516,783,059.1</t>
-  </si>
-  <si>
-    <t>292,064,782.0</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>242,879,748.0</t>
-  </si>
-  <si>
-    <t>218,385,819.0</t>
+    <t>252,410,960.2</t>
+  </si>
+  <si>
+    <t>233,323,400.0</t>
+  </si>
+  <si>
+    <t>197,990,885.0</t>
+  </si>
+  <si>
+    <t>183,001,392.5</t>
+  </si>
+  <si>
+    <t>165,086,622.19</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>3,953,821,420.6</t>
+    <t>2,277,179,978.71</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,643,309,582.88</t>
+    <t>1,774,226,159.28</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,017,892,771.2</t>
+    <t>1,269,047,454.59</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>624,374,282.79</t>
+    <t>878,083,202.0</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>620,402,475.6</t>
+    <t>827,982,174.0</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>279,478,970.5</t>
+    <t>423,956,811.5</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>213,228,349.8</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>154,211,746.19</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>132,068,890.8</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>218,177,441.1</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>214,963,759.0</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>167,992,513.0</t>
+    <t>111,329,250.3</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>125,203,896.5</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>122,421,124.6</t>
+    <t>93,018,197.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>70,247,430.5</t>
+    <t>54,285,440.7</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>28,995,470.83</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>37,283,861.0</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>18,367,859.89</t>
+    <t>17,810,329.89</t>
+  </si>
+  <si>
+    <t>Tradings</t>
+  </si>
+  <si>
+    <t>2,220,431.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -674,196 +626,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>1,941,299,354.0</t>
-  </si>
-  <si>
-    <t>4,867,825.0</t>
-  </si>
-  <si>
-    <t>4,625,127.2</t>
-  </si>
-  <si>
-    <t>125,453,529.8</t>
-  </si>
-  <si>
-    <t>107,201,955.0</t>
-  </si>
-  <si>
-    <t>101,684,542.2</t>
-  </si>
-  <si>
-    <t>37,632,633.19</t>
-  </si>
-  <si>
-    <t>9,130,539.0</t>
-  </si>
-  <si>
-    <t>74,395,815.0</t>
-  </si>
-  <si>
-    <t>64,088,043.0</t>
-  </si>
-  <si>
-    <t>12,193,005.5</t>
-  </si>
-  <si>
-    <t>1,008,582.5</t>
-  </si>
-  <si>
-    <t>852,671.0</t>
-  </si>
-  <si>
-    <t>150,015,209.19</t>
-  </si>
-  <si>
-    <t>101,113,572.9</t>
-  </si>
-  <si>
-    <t>19,244,015.0</t>
-  </si>
-  <si>
-    <t>18,619,020.7</t>
-  </si>
-  <si>
-    <t>3,597,372.4</t>
-  </si>
-  <si>
-    <t>43,418,605.0</t>
-  </si>
-  <si>
-    <t>3,783,065.5</t>
-  </si>
-  <si>
-    <t>1,736,649.0</t>
-  </si>
-  <si>
-    <t>1,680,664.0</t>
-  </si>
-  <si>
-    <t>464,360.0</t>
-  </si>
-  <si>
-    <t>108,920,126.0</t>
-  </si>
-  <si>
-    <t>58,752,733.2</t>
-  </si>
-  <si>
-    <t>39,785,792.5</t>
-  </si>
-  <si>
-    <t>29,250,895.0</t>
-  </si>
-  <si>
-    <t>26,668,114.6</t>
-  </si>
-  <si>
-    <t>94,763,330.8</t>
-  </si>
-  <si>
-    <t>64,520,056.0</t>
-  </si>
-  <si>
-    <t>64,301,113.9</t>
-  </si>
-  <si>
-    <t>16,908,800.0</t>
-  </si>
-  <si>
-    <t>1,418,946.0</t>
-  </si>
-  <si>
-    <t>40,726,000.0</t>
-  </si>
-  <si>
-    <t>17,942,910.0</t>
-  </si>
-  <si>
-    <t>4,874,917.0</t>
-  </si>
-  <si>
-    <t>162,200.0</t>
-  </si>
-  <si>
-    <t>181,476,047.5</t>
-  </si>
-  <si>
-    <t>167,791,092.5</t>
-  </si>
-  <si>
-    <t>125,925,549.2</t>
-  </si>
-  <si>
-    <t>77,152,449.4</t>
-  </si>
-  <si>
-    <t>35,649,467.0</t>
-  </si>
-  <si>
-    <t>119,156,244.4</t>
-  </si>
-  <si>
-    <t>54,272,482.1</t>
-  </si>
-  <si>
-    <t>22,574,340.0</t>
-  </si>
-  <si>
-    <t>114,507,018.7</t>
-  </si>
-  <si>
-    <t>29,710,348.0</t>
-  </si>
-  <si>
-    <t>21,696,520.5</t>
-  </si>
-  <si>
-    <t>20,389,324.1</t>
-  </si>
-  <si>
-    <t>13,866,041.0</t>
-  </si>
-  <si>
-    <t>446,052,135.0</t>
-  </si>
-  <si>
-    <t>2,598,547.79</t>
-  </si>
-  <si>
-    <t>404,490.0</t>
-  </si>
-  <si>
-    <t>305,590.0</t>
-  </si>
-  <si>
-    <t>119,502,693.0</t>
-  </si>
-  <si>
-    <t>35,164,636.79</t>
-  </si>
-  <si>
-    <t>31,781,005.2</t>
-  </si>
-  <si>
-    <t>16,806,335.3</t>
-  </si>
-  <si>
-    <t>14,530,230.8</t>
-  </si>
-  <si>
-    <t>220,922,547.8</t>
-  </si>
-  <si>
-    <t>23,768,883.7</t>
-  </si>
-  <si>
-    <t>6,818,076.8</t>
-  </si>
-  <si>
-    <t>1,031,808.0</t>
-  </si>
-  <si>
-    <t>415,950.0</t>
+    <t>195,649,415.5</t>
+  </si>
+  <si>
+    <t>82,008,244.0</t>
+  </si>
+  <si>
+    <t>61,828,104.5</t>
+  </si>
+  <si>
+    <t>43,634,445.0</t>
+  </si>
+  <si>
+    <t>42,371,753.4</t>
+  </si>
+  <si>
+    <t>90,816,454.1</t>
+  </si>
+  <si>
+    <t>80,087,646.5</t>
+  </si>
+  <si>
+    <t>59,183,832.5</t>
+  </si>
+  <si>
+    <t>18,912,793.8</t>
+  </si>
+  <si>
+    <t>18,083,758.89</t>
+  </si>
+  <si>
+    <t>81,848,972.4</t>
+  </si>
+  <si>
+    <t>50,555,715.1</t>
+  </si>
+  <si>
+    <t>36,292,261.0</t>
+  </si>
+  <si>
+    <t>34,920,518.2</t>
+  </si>
+  <si>
+    <t>25,525,154.1</t>
+  </si>
+  <si>
+    <t>81,906,921.0</t>
+  </si>
+  <si>
+    <t>30,538,157.2</t>
+  </si>
+  <si>
+    <t>28,398,138.2</t>
+  </si>
+  <si>
+    <t>12,403,041.2</t>
+  </si>
+  <si>
+    <t>9,379,939.0</t>
+  </si>
+  <si>
+    <t>69,970,512.09</t>
+  </si>
+  <si>
+    <t>40,087,623.5</t>
+  </si>
+  <si>
+    <t>39,950,712.1</t>
+  </si>
+  <si>
+    <t>29,413,828.1</t>
+  </si>
+  <si>
+    <t>25,992,139.6</t>
+  </si>
+  <si>
+    <t>88,060,551.6</t>
+  </si>
+  <si>
+    <t>60,485,285.5</t>
+  </si>
+  <si>
+    <t>39,468,393.29</t>
+  </si>
+  <si>
+    <t>37,213,241.2</t>
+  </si>
+  <si>
+    <t>24,109,086.7</t>
+  </si>
+  <si>
+    <t>68,471,193.3</t>
+  </si>
+  <si>
+    <t>53,169,410.5</t>
+  </si>
+  <si>
+    <t>40,752,062.2</t>
+  </si>
+  <si>
+    <t>26,207,027.0</t>
+  </si>
+  <si>
+    <t>23,106,522.2</t>
+  </si>
+  <si>
+    <t>202,038,224.4</t>
+  </si>
+  <si>
+    <t>83,087,582.09</t>
+  </si>
+  <si>
+    <t>68,798,665.7</t>
+  </si>
+  <si>
+    <t>60,416,724.0</t>
+  </si>
+  <si>
+    <t>41,763,449.7</t>
+  </si>
+  <si>
+    <t>90,271,340.8</t>
+  </si>
+  <si>
+    <t>86,410,507.4</t>
+  </si>
+  <si>
+    <t>39,622,863.2</t>
+  </si>
+  <si>
+    <t>37,379,154.2</t>
+  </si>
+  <si>
+    <t>35,362,310.5</t>
+  </si>
+  <si>
+    <t>103,693,267.5</t>
+  </si>
+  <si>
+    <t>86,389,504.6</t>
+  </si>
+  <si>
+    <t>49,199,041.0</t>
+  </si>
+  <si>
+    <t>45,929,743.8</t>
+  </si>
+  <si>
+    <t>23,411,077.7</t>
+  </si>
+  <si>
+    <t>251,305,626.7</t>
+  </si>
+  <si>
+    <t>30,951,269.3</t>
+  </si>
+  <si>
+    <t>28,338,818.4</t>
+  </si>
+  <si>
+    <t>13,106,630.8</t>
+  </si>
+  <si>
+    <t>12,945,212.0</t>
+  </si>
+  <si>
+    <t>70,475,696.9</t>
+  </si>
+  <si>
+    <t>46,865,633.6</t>
+  </si>
+  <si>
+    <t>39,437,404.2</t>
+  </si>
+  <si>
+    <t>33,487,388.6</t>
+  </si>
+  <si>
+    <t>23,465,669.2</t>
+  </si>
+  <si>
+    <t>63,637,510.1</t>
+  </si>
+  <si>
+    <t>54,271,914.18</t>
+  </si>
+  <si>
+    <t>25,353,664.1</t>
+  </si>
+  <si>
+    <t>24,360,267.9</t>
+  </si>
+  <si>
+    <t>17,223,372.5</t>
+  </si>
+  <si>
+    <t>67,512,785.2</t>
+  </si>
+  <si>
+    <t>54,964,502.2</t>
+  </si>
+  <si>
+    <t>37,670,108.7</t>
+  </si>
+  <si>
+    <t>27,430,200.6</t>
+  </si>
+  <si>
+    <t>21,331,962.89</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1450,27 +1420,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1480,37 +1450,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1520,37 +1490,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1560,128 +1530,128 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.9154666392308918</v>
+        <v>0.07377230300071143</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.08601520227977112</v>
+        <v>0.03459185334986548</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>73</v>
@@ -1690,82 +1660,82 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1318824129960666</v>
+        <v>0.02578752283022435</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2410366583982928</v>
+        <v>0.1086544137844791</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="O9" s="17" t="s">
         <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.08458897402471381</v>
+        <v>0.02048138986583458</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1597361817262815</v>
+        <v>0.04137879577909132</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="V9" s="18">
-        <v>0.08685622935390444</v>
+        <v>0.01497514757521542</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.03182238318769257</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.01431662927391281</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>65</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.0779524207273137</v>
+        <v>0.0249427120968082</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.07964317167495914</v>
+        <v>0.0140877597399061</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1423932255440694</v>
+        <v>0.02547751695073601</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>92</v>
@@ -1774,37 +1744,37 @@
         <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.004535653132094384</v>
+        <v>0.01870936893441867</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.07954021602588975</v>
+        <v>0.02160473146100229</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08529548896206493</v>
+        <v>0.0130206791212635</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01348867297446854</v>
+        <v>0.03070913502442324</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
@@ -1813,7 +1783,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04220586690721</v>
+        <v>0.02384010286078295</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1822,16 +1792,16 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01447476914436108</v>
+        <v>0.01290142567241726</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0372337392115436</v>
+        <v>0.008657175580914792</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>94</v>
@@ -1840,37 +1810,37 @@
         <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.002328786366120291</v>
+        <v>0.01564017785049531</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05443452790906617</v>
+        <v>0.0202044616432841</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07069623269066977</v>
+        <v>0.01219527977516374</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.001951850786059108</v>
+        <v>0.02493627756704901</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
@@ -1879,64 +1849,64 @@
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02943156482273845</v>
+        <v>0.02099677433254153</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01023827731461391</v>
+        <v>0.01162879770327451</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03556653765913924</v>
+        <v>0.00684303326404462</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.001925467684940757</v>
+        <v>0.01421272865045266</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04575071200612815</v>
+        <v>0.0108018362759515</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0705759090745891</v>
+        <v>0.01031613233287769</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.001919760734545573</v>
+        <v>0.01596825326742368</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1945,16 +1915,16 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02151759761224069</v>
+        <v>0.01620786639380277</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.009710179815856788</v>
+        <v>0.008907437571207927</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>89</v>
@@ -1963,656 +1933,667 @@
         <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03379014720022352</v>
+        <v>0.005466329730244357</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.001499763785309971</v>
+        <v>0.01299186356576033</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0427365749735326</v>
+        <v>0.0105230112232401</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="V13" s="18">
-        <v>0.04961391599977941</v>
+        <v>0.009962580890694473</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D16" s="10">
-        <v>0.01918552197728107</v>
+        <v>0.08770770146000822</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1787073133029209</v>
+        <v>0.01613434459875363</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2700053732997748</v>
+        <v>0.02258756719943275</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.2412463963376754</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.02669928657164646</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.1165220476287693</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.8876939812071724</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="S16" s="16">
-        <v>0.2335464612954104</v>
+        <v>0.0297990142848627</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="V16" s="18">
-        <v>0.436201287923751</v>
+        <v>0.01830390346263877</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D17" s="10">
-        <v>0.01722172518244906</v>
+        <v>0.02861638068614083</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08125747408300255</v>
+        <v>0.015885837305908</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1431331611066848</v>
+        <v>0.02043243022673608</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L17" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.1257648685171983</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.01675143273941567</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.08653237740870645</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="O17" s="17" t="s">
+      <c r="S17" s="16">
+        <v>0.01163901117050298</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="P17" s="18">
-        <v>0.003150046186163919</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.03445610120755575</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>86</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.03778374682776002</v>
+        <v>0.01746775706699817</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.01958995438172294</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="10">
-        <v>0.007843994051225643</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07648089806257824</v>
+        <v>0.01330589024299117</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J18" s="14">
-        <v>0.1065294209692933</v>
+        <v>0.01894079058590392</v>
       </c>
       <c r="K18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.08235178452790358</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.01526500765032522</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="R18" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.05642377999479312</v>
-      </c>
-      <c r="N18" s="17" t="s">
+      <c r="S18" s="16">
+        <v>0.01082683909673617</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="O18" s="17" t="s">
+      <c r="U18" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.001258112670846421</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.02737740394368966</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>172</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.008464844895567515</v>
+        <v>0.01683370421207177</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.01578731157158405</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="10">
-        <v>0.0008814765412396458</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="G19" s="12">
+        <v>0.01148155857909186</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.05022676471920086</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="13" t="s">
+      <c r="J19" s="14">
+        <v>0.01349024727216496</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.007689840483272037</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.09240002687931091</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="L19" s="15" t="s">
+      <c r="P19" s="18">
+        <v>0.01463808494755032</v>
+      </c>
+      <c r="Q19" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.03882781215091773</v>
-      </c>
-      <c r="N19" s="17" t="s">
+      <c r="R19" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.01041748508868693</v>
+      </c>
+      <c r="T19" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="O19" s="17" t="s">
+      <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="P19" s="18">
-        <v>0.0008787429239746855</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.0272107621450222</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>174</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.006628401301753702</v>
+        <v>0.01387064809516726</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.01521514703998627</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0.0005257135155979379</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>134</v>
-      </c>
       <c r="G20" s="12">
-        <v>0.04016100845450209</v>
+        <v>0.01016615524822157</v>
       </c>
       <c r="H20" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.01155115934675643</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.006311257476680684</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="O20" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.05962391114999782</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" s="15" t="s">
+      <c r="P20" s="18">
+        <v>0.01415238193144235</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.031340663737206</v>
-      </c>
-      <c r="N20" s="17" t="s">
+      <c r="R20" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.008669116112851065</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="O20" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.0005946665476897656</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.02610825488621172</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>176</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.00463302434509814</v>
+        <v>0.01245379092483899</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.4788074509856127</v>
+        <v>0.2757663093648107</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.199004656219299</v>
+        <v>0.2148586429247316</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1232667314248587</v>
+        <v>0.1536815430638739</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07561167463225263</v>
+        <v>0.1063358040179527</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07513068910485123</v>
+        <v>0.1002685736206834</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03384488049257453</v>
+        <v>0.05134113523303696</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.02642127029090805</v>
+        <v>0.02582193573884615</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02603209365117363</v>
+        <v>0.01867502986486861</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02034387959838386</v>
+        <v>0.0159935318851222</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01516218163630015</v>
+        <v>0.01348196311511537</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01482518818657798</v>
+        <v>0.01126449608081954</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.008506958093946948</v>
+        <v>0.006573962433349674</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.004515072520802636</v>
+        <v>0.003511349148422889</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002224346333134399</v>
+        <v>0.00215682949568768</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>218</v>
+        <v>198</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" s="22">
+        <v>0.0002688940126785237</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2775,27 +2756,27 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2805,37 +2786,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2845,37 +2826,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2885,835 +2866,835 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="U8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="V8" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.9164577121222572</v>
+        <v>0.1936099662757753</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1258529916254445</v>
+        <v>0.1407103752303289</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1320169483182046</v>
+        <v>0.1314154361853304</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2982628036822352</v>
+        <v>0.1531759496729625</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="P9" s="18">
-        <v>0.08655578927541265</v>
+        <v>0.1399440829858106</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="S9" s="16">
-        <v>0.2177903252666971</v>
+        <v>0.1762058189296764</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1911932215975946</v>
+        <v>0.1385519584484206</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="D10" s="10">
-        <v>0.01431662927391281</v>
+        <v>0.08115339018314396</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1075433012236079</v>
+        <v>0.1240872361953288</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1137255887383702</v>
+        <v>0.08117146931374054</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M10" s="16">
-        <v>0.2010357343386092</v>
+        <v>0.05711008512177154</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="P10" s="18">
-        <v>0.007541610796410515</v>
+        <v>0.08017699944471227</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1174785353621008</v>
+        <v>0.1210287588605427</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1301747971515709</v>
+        <v>0.1075886894806464</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01348867297446854</v>
+        <v>0.06118360842810754</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G11" s="12">
-        <v>0.1020083201990045</v>
+        <v>0.09169901380948033</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02163674632688794</v>
+        <v>0.05827028940765121</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03826127963032558</v>
+        <v>0.05310798812384894</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="P11" s="18">
-        <v>0.003462041788061963</v>
+        <v>0.07990317065958175</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07955334801548355</v>
+        <v>0.07897475585725325</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="V11" s="18">
-        <v>0.1297330625155154</v>
+        <v>0.0824620947364423</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D12" s="10">
-        <v>0.00229802567714218</v>
+        <v>0.04317959960842395</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03775246083959148</v>
+        <v>0.02930334969169247</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="J12" s="14">
-        <v>0.001789750993078651</v>
+        <v>0.05606784051782146</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03701865527778483</v>
+        <v>0.02319520244989895</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="P12" s="18">
-        <v>0.003350434658754516</v>
+        <v>0.05882894203595188</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05848838199463711</v>
+        <v>0.07446228216305624</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03411496744634695</v>
+        <v>0.05303011005009953</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.00218345176041635</v>
+        <v>0.04193007030383625</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12">
-        <v>0.009159611930686339</v>
+        <v>0.02801884884860088</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J13" s="14">
-        <v>0.001513082736433923</v>
+        <v>0.0409827901486186</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="M13" s="16">
-        <v>0.007152357308535431</v>
+        <v>0.01754163197270543</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0009257102181871255</v>
+        <v>0.0519854154556227</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="S13" s="16">
-        <v>0.05332400508776087</v>
+        <v>0.048241366746334</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="V13" s="18">
-        <v>0.002862846363912532</v>
+        <v>0.04675621600042873</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D16" s="10">
-        <v>0.01922612126099283</v>
+        <v>0.1999321782410412</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1820538929645666</v>
+        <v>0.1398657805173314</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2700053732997748</v>
+        <v>0.1664882964125601</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M16" s="16">
-        <v>0.2276648122606234</v>
+        <v>0.4699722264975812</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="P16" s="18">
-        <v>0.8892131518943991</v>
+        <v>0.1409544746701438</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="S16" s="16">
-        <v>0.2389506084368306</v>
+        <v>0.1273362405535517</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="V16" s="18">
-        <v>0.4457303608985279</v>
+        <v>0.1366126126761624</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="D17" s="10">
-        <v>0.01722172518244906</v>
+        <v>0.0822214772643505</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1683253631276199</v>
+        <v>0.133883832402317</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14">
-        <v>0.2114452776509829</v>
+        <v>0.1387056440166573</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="M17" s="16">
-        <v>0.05907062183968805</v>
+        <v>0.05788265522288536</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="P17" s="18">
-        <v>0.005180252930716846</v>
+        <v>0.09373331594783334</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="S17" s="16">
-        <v>0.07031315485769148</v>
+        <v>0.1085960388529751</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04795578004716518</v>
+        <v>0.1112210706126619</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D18" s="10">
-        <v>0.008470573182612604</v>
+        <v>0.06808150850823953</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12">
-        <v>0.1263265140021361</v>
+        <v>0.06139138555699228</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="J18" s="14">
-        <v>0.1065294209692933</v>
+        <v>0.07899321449410104</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M18" s="16">
-        <v>0.04313739299494369</v>
+        <v>0.05299705285014465</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="P18" s="18">
-        <v>0.001258112670846421</v>
+        <v>0.07887653242014442</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06354744264444381</v>
+        <v>0.05073171885069633</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01375606004439661</v>
+        <v>0.07622573937746589</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D19" s="10">
-        <v>0.002301373701794318</v>
+        <v>0.0597869401563984</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="G19" s="12">
-        <v>0.07739811373741617</v>
+        <v>0.05791499861338812</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="J19" s="14">
-        <v>0.09630766817322164</v>
+        <v>0.07374408179323062</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04053840276384302</v>
+        <v>0.02451100096660818</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="O19" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.06697624111309726</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.04874397078686715</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="P19" s="18">
-        <v>0.0008063582697788577</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.03360496692345154</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>281</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.002081761942354298</v>
+        <v>0.05550521074039822</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D20" s="10">
-        <v>7.657213741916803E-05</v>
+        <v>0.04132810756072532</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03576297995724118</v>
+        <v>0.05479011516996016</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="J20" s="14">
-        <v>0.04005864411993577</v>
+        <v>0.03758846198433351</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0275686997784277</v>
+        <v>0.02420912808842894</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="O20" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.04693236421007101</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.03446331417362332</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.0006091992970449731</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.02905380124268477</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>282</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.0008392151252192949</v>
+        <v>0.04316538232938975</v>
       </c>
     </row>
   </sheetData>
